--- a/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
+++ b/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
@@ -1636,12 +1636,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>技术文档 4.3</t>
+          <t>多篇对比接口 POST /knowledge-bases/{id}/compare + KB 页面对照表面板；技术文档 5.7；实测 1599 字对照表 + 8 条引用</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
@@ -1650,11 +1650,11 @@
         </is>
       </c>
       <c r="K8" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>知识库级跨文档检索已具备；对比问答的专门 UI 未实现</t>
+          <t>证据充分时生成对照表；证据不足走固定说明（技术文档 5.7）</t>
         </is>
       </c>
     </row>

--- a/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
+++ b/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
@@ -1524,12 +1524,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>技术文档 4.2</t>
+          <t>技术文档 4.3.5 + 评测报告 §6；A/B 实测 top-3 近重复对 1→0、hit@1 不变；单测 internal/retrieval/dedupe_test.go</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -1538,11 +1538,11 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>按版面块切分并记录页码；尚未实现语义去重 v1/v7 的实验对比</t>
+          <t>阈值 0.85 与归一化方式已写入文档；更大评测集待补</t>
         </is>
       </c>
     </row>

--- a/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
+++ b/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
@@ -1860,12 +1860,12 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>技术文档 4.8/6.1；用量页</t>
+          <t>技术文档 4.10 + 评测报告 §7；检索 avg 154ms/P95 178ms；token 用量与库规模数据</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
@@ -1874,11 +1874,11 @@
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>token 记账与解析耗时数据；优化前后对比数据待补</t>
+          <t>优化：召回池夹取、近重复抑制、解析缓存、上下文预算、写作/翻译上限</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>README §1.4；技术文档 1.1</t>
+          <t>技术文档 1.6 能力对比表（8 个维度，对比通用文档问答/学术检索工具形态）</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="K16" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>与通用 RAG/聊天工具差异明确；与 RAGFlow/PaperQA 的正式对比待补</t>
+          <t>对比维度覆盖溯源/校验/拒答/解析/阅读/引用图谱/写作/BYOK</t>
         </is>
       </c>
     </row>

--- a/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
+++ b/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>技术文档 4.3.5 + 评测报告 §6；A/B 实测 top-3 近重复对 1→0、hit@1 不变；单测 internal/retrieval/dedupe_test.go</t>
+          <t>技术文档 4.3.5/4.3.6 + 评测报告 §6；检索期去重 A/B（1→0）+ 上传 SimHash 去重（v7→v1 distance=6）+ 版本差异摘要；单测 dedupe/fingerprint</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>阈值 0.85 与归一化方式已写入文档；更大评测集待补</t>
+          <t>阈值 0.85（检索）/14（指纹）与归一化方式已写入文档；更大评测集待补</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>技术文档 4.10 + 评测报告 §7；检索 avg 154ms/P95 178ms；token 用量与库规模数据</t>
+          <t>技术文档 4.10 + 评测报告 §7；检索 avg 154ms/P95 178ms、解析耗时、token 用量与库规模；去重/缓存/上下文预算等优化</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
@@ -1874,11 +1874,11 @@
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>优化：召回池夹取、近重复抑制、解析缓存、上下文预算、写作/翻译上限</t>
+          <t>单机数据；未做并发压测（已知限制）</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>go test ./...；web vitest 171 用例</t>
+          <t>go test ./... 全绿；web vitest 171 用例 + tsc/oxlint；关键链路有单测/集成测试</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
@@ -2602,11 +2602,11 @@
         </is>
       </c>
       <c r="K25" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>核心链路有测试；覆盖率未量化</t>
+          <t>覆盖率未量化（已知限制）</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>技术文档 7.3</t>
+          <t>技术文档 7.3；Roadmap 已更新（实体消歧、Future Work 自动挖掘、多用户推荐）</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>Roadmap 明确（实体消歧、划词翻译、多篇对比等）</t>
+          <t>划词翻译/引用图谱/自动综述已从 Roadmap 落地</t>
         </is>
       </c>
     </row>

--- a/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
+++ b/docs/competition/submission/评审自检清单_陈晓乐_已填.xlsx
@@ -2644,12 +2644,12 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml</t>
+          <t>GitHub Actions CI 在 main 上通过（run 40967156246，c718d44）；ci.yml 跑 Go/Web 测试与契约检查</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
@@ -2658,11 +2658,11 @@
         </is>
       </c>
       <c r="K26" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>CI 配置存在并在 GitHub 运行；参赛分支的 CI 结果需最终确认</t>
+          <t>期间 14e4f38 因并发新提交被自动取消；最终以最新成功运行为准</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已通过</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>docs/competition 快速开始；测试数据目录</t>
+          <t>scripts/seed-demo.mjs（dry-run/真实执行）+ docs/competition/README §5.0；四个演示库 + Agent 可由官方 pdf 目录复现</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
@@ -2938,11 +2938,11 @@
         </is>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>有测试 PDF/演示库；一键种子脚本待补</t>
+          <t>演示数据依赖用户提供 PDF；脚本不包含版权文件</t>
         </is>
       </c>
     </row>
